--- a/Calendario-Champions-26-27.xlsx
+++ b/Calendario-Champions-26-27.xlsx
@@ -10,17 +10,390 @@
     <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$G$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$I$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="36">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="31"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="32"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="33"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="34"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="35"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="36">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
+    <bk>
+      <rc t="1" v="14"/>
+    </bk>
+    <bk>
+      <rc t="1" v="15"/>
+    </bk>
+    <bk>
+      <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
+    </bk>
+    <bk>
+      <rc t="1" v="18"/>
+    </bk>
+    <bk>
+      <rc t="1" v="19"/>
+    </bk>
+    <bk>
+      <rc t="1" v="20"/>
+    </bk>
+    <bk>
+      <rc t="1" v="21"/>
+    </bk>
+    <bk>
+      <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
+    </bk>
+    <bk>
+      <rc t="1" v="26"/>
+    </bk>
+    <bk>
+      <rc t="1" v="27"/>
+    </bk>
+    <bk>
+      <rc t="1" v="28"/>
+    </bk>
+    <bk>
+      <rc t="1" v="29"/>
+    </bk>
+    <bk>
+      <rc t="1" v="30"/>
+    </bk>
+    <bk>
+      <rc t="1" v="31"/>
+    </bk>
+    <bk>
+      <rc t="1" v="32"/>
+    </bk>
+    <bk>
+      <rc t="1" v="33"/>
+    </bk>
+    <bk>
+      <rc t="1" v="34"/>
+    </bk>
+    <bk>
+      <rc t="1" v="35"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="hh:mm"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -102,58 +475,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -228,6 +589,245 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="36">
+  <rv s="0">
+    <v>0</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>14</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>15</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>16</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>18</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>19</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>20</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>21</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>22</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>25</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>26</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>27</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>28</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>29</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>30</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>31</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>32</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>33</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>34</v>
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>35</v>
+    <v>4</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
+  <rel r:id="rId15"/>
+  <rel r:id="rId16"/>
+  <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
+  <rel r:id="rId19"/>
+  <rel r:id="rId20"/>
+  <rel r:id="rId21"/>
+  <rel r:id="rId22"/>
+  <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
+  <rel r:id="rId27"/>
+  <rel r:id="rId28"/>
+  <rel r:id="rId29"/>
+  <rel r:id="rId30"/>
+  <rel r:id="rId31"/>
+  <rel r:id="rId32"/>
+  <rel r:id="rId33"/>
+  <rel r:id="rId34"/>
+  <rel r:id="rId35"/>
+  <rel r:id="rId36"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,16 +1119,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="6.5" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6.5" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -554,28 +1156,38 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Escudo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Gol</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gol</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Escudo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Equipo Visitante</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="21" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="3" t="n">
         <v>46273.78125</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="4" t="n">
         <v>46273.78125</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -583,22 +1195,28 @@
           <t>AEK</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n"/>
+      <c r="E2" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="2" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>LASK</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="21" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="3" t="n">
         <v>46273.78125</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="4" t="n">
         <v>46273.78125</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -606,22 +1224,28 @@
           <t>Brugge</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n"/>
+      <c r="E3" s="2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="21" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="3" t="n">
         <v>46273.875</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="4" t="n">
         <v>46273.875</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -629,22 +1253,28 @@
           <t>Borussia Dortmund</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="2" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Villarreal</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="3" t="n">
         <v>46273.875</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="4" t="n">
         <v>46273.875</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -652,22 +1282,28 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
+      <c r="E5" s="2" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="2" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="21" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="3" t="n">
         <v>46273.875</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="4" t="n">
         <v>46273.875</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -675,22 +1311,28 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="2" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Betis</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="3" t="n">
         <v>46273.875</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="4" t="n">
         <v>46273.875</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -698,22 +1340,28 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
+      <c r="E7" s="2" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Inter Milan</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="21" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="3" t="n">
         <v>46274.78125</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="4" t="n">
         <v>46274.78125</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -721,22 +1369,28 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="2" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="3" t="n">
         <v>46274.78125</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="4" t="n">
         <v>46274.78125</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -744,22 +1398,28 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
+      <c r="E9" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Viking</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="21" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="3" t="n">
         <v>46274.875</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="4" t="n">
         <v>46274.875</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -767,22 +1427,28 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
+      <c r="E10" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="2" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="3" t="n">
         <v>46274.875</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="4" t="n">
         <v>46274.875</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -790,22 +1456,28 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
+      <c r="E11" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Slovan Bratislava</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="3" t="n">
         <v>46274.875</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="4" t="n">
         <v>46274.875</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -813,22 +1485,28 @@
           <t>Sporting Portugal</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="2" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="2" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Galatasaray</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="21" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="3" t="n">
         <v>46274.875</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="4" t="n">
         <v>46274.875</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -836,22 +1514,28 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="2" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
       <c r="F13" s="6" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="21" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="3" t="n">
         <v>46275.78125</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="4" t="n">
         <v>46275.78125</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -859,22 +1543,28 @@
           <t>Fenerbahçe</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="2" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="2" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="21" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="3" t="n">
         <v>46275.78125</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="4" t="n">
         <v>46275.78125</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -882,22 +1572,28 @@
           <t>PSV Eindhoven</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
+      <c r="E15" s="2" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="2" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="21" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="3" t="n">
         <v>46275.875</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="4" t="n">
         <v>46275.875</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -905,22 +1601,28 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="2" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="2" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="21" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="3" t="n">
         <v>46275.875</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="4" t="n">
         <v>46275.875</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -928,22 +1630,28 @@
           <t>Bayern München</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="2" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="21" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="3" t="n">
         <v>46275.875</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="4" t="n">
         <v>46275.875</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -951,22 +1659,28 @@
           <t>Manchester United</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
+      <c r="E18" s="2" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="2" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Sabah</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="21" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="3" t="n">
         <v>46275.875</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="4" t="n">
         <v>46275.875</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -974,22 +1688,28 @@
           <t>Slavia Praha</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
+      <c r="E19" s="2" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="2" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="21" customHeight="1">
       <c r="A20" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="9" t="n">
         <v>46308.78125</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="10" t="n">
         <v>46308.78125</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -997,22 +1717,28 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
+      <c r="E20" s="8" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="8" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>Sporting Portugal</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="21" customHeight="1">
       <c r="A21" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="9" t="n">
         <v>46308.78125</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="10" t="n">
         <v>46308.78125</v>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1020,22 +1746,28 @@
           <t>Sabah</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
+      <c r="E21" s="8" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="8" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Slavia Praha</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="21" customHeight="1">
       <c r="A22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1043,22 +1775,28 @@
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
+      <c r="E22" s="8" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="8" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C23" s="18" t="n">
+      <c r="C23" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1066,22 +1804,28 @@
           <t>Atlético Madrid</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
+      <c r="E23" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="8" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>Manchester United</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1089,22 +1833,28 @@
           <t>Inter Milan</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
+      <c r="E24" s="8" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="8" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>Brugge</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1112,22 +1862,28 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
+      <c r="E25" s="8" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="8" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="21" customHeight="1">
       <c r="A26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1135,22 +1891,28 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
+      <c r="E26" s="8" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="8" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="21" customHeight="1">
       <c r="A27" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1158,22 +1920,28 @@
           <t>Viking</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
+      <c r="E27" s="8" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="8" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>Bayern München</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="9" t="n">
         <v>46308.875</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="10" t="n">
         <v>46308.875</v>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1181,22 +1949,28 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
+      <c r="E28" s="8" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
       <c r="F28" s="6" t="n"/>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="8" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="21" customHeight="1">
       <c r="A29" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="9" t="n">
         <v>46309.78125</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="10" t="n">
         <v>46309.78125</v>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1204,22 +1978,28 @@
           <t>Feyenoord</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n"/>
+      <c r="E29" s="8" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
       <c r="F29" s="6" t="n"/>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="8" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="21" customHeight="1">
       <c r="A30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="9" t="n">
         <v>46309.78125</v>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="10" t="n">
         <v>46309.78125</v>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1227,22 +2007,28 @@
           <t>LASK</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
+      <c r="E30" s="8" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="F30" s="6" t="n"/>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="8" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="21" customHeight="1">
       <c r="A31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C31" s="18" t="n">
+      <c r="C31" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -1250,22 +2036,28 @@
           <t>Roma</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n"/>
+      <c r="E31" s="8" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
       <c r="F31" s="6" t="n"/>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="8" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="21" customHeight="1">
       <c r="A32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C32" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1273,22 +2065,28 @@
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
+      <c r="E32" s="8" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="8" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="21" customHeight="1">
       <c r="A33" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="17" t="n">
+      <c r="B33" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -1296,22 +2094,28 @@
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n"/>
+      <c r="E33" s="8" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="8" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>AEK</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B34" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C34" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -1319,22 +2123,28 @@
           <t>Bodø/Glimt</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n"/>
+      <c r="E34" s="8" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
       <c r="F34" s="6" t="n"/>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="8" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B35" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C35" s="18" t="n">
+      <c r="C35" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -1342,22 +2152,28 @@
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n"/>
+      <c r="E35" s="8" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
       <c r="F35" s="6" t="n"/>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="8" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -1365,22 +2181,28 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n"/>
+      <c r="E36" s="8" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
       <c r="F36" s="6" t="n"/>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="8" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="17" t="n">
+      <c r="B37" s="9" t="n">
         <v>46309.875</v>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C37" s="10" t="n">
         <v>46309.875</v>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -1388,22 +2210,28 @@
           <t>Slovan Bratislava</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n"/>
+      <c r="E37" s="8" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
       <c r="F37" s="6" t="n"/>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="8" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="21" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="15" t="n">
+      <c r="B38" s="3" t="n">
         <v>46315.78125</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="4" t="n">
         <v>46315.78125</v>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1411,22 +2239,28 @@
           <t>Fenerbahçe</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n"/>
+      <c r="E38" s="2" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
       <c r="F38" s="6" t="n"/>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="2" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Slavia Praha</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="15" t="n">
+      <c r="B39" s="3" t="n">
         <v>46315.78125</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="4" t="n">
         <v>46315.78125</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1434,22 +2268,28 @@
           <t>Sabah</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n"/>
+      <c r="E39" s="2" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
       <c r="F39" s="6" t="n"/>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="2" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="21" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1457,22 +2297,28 @@
           <t>Roma</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n"/>
+      <c r="E40" s="2" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
       <c r="F40" s="6" t="n"/>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Slovan Bratislava</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="21" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1480,22 +2326,28 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n"/>
+      <c r="E41" s="2" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
       <c r="F41" s="6" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="2" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="21" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B42" s="15" t="n">
+      <c r="B42" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1503,22 +2355,28 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n"/>
+      <c r="E42" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
       <c r="F42" s="6" t="n"/>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Villarreal</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="21" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="15" t="n">
+      <c r="B43" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1526,22 +2384,28 @@
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n"/>
+      <c r="E43" s="2" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
       <c r="F43" s="6" t="n"/>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>AEK</t>
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="21" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="15" t="n">
+      <c r="B44" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1549,22 +2413,28 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n"/>
+      <c r="E44" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
       <c r="F44" s="6" t="n"/>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="21" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="15" t="n">
+      <c r="B45" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1572,22 +2442,28 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n"/>
+      <c r="E45" s="2" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
       <c r="F45" s="6" t="n"/>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="21" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="3" t="n">
         <v>46315.875</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="4" t="n">
         <v>46315.875</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1595,22 +2471,28 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n"/>
+      <c r="E46" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
       <c r="F46" s="6" t="n"/>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="2" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="21" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="15" t="n">
+      <c r="B47" s="3" t="n">
         <v>46316.78125</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="4" t="n">
         <v>46316.78125</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1618,22 +2500,28 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n"/>
+      <c r="E47" s="2" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
       <c r="F47" s="6" t="n"/>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="2" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Manchester United</t>
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="21" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="15" t="n">
+      <c r="B48" s="3" t="n">
         <v>46316.78125</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="4" t="n">
         <v>46316.78125</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1641,22 +2529,28 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n"/>
+      <c r="E48" s="2" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
       <c r="F48" s="6" t="n"/>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="2" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Galatasaray</t>
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="21" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B49" s="15" t="n">
+      <c r="B49" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1664,22 +2558,28 @@
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n"/>
+      <c r="E49" s="2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
       <c r="F49" s="6" t="n"/>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Viking</t>
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="21" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="15" t="n">
+      <c r="B50" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1687,22 +2587,28 @@
           <t>Brugge</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n"/>
+      <c r="E50" s="2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="F50" s="6" t="n"/>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="2" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="21" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B51" s="15" t="n">
+      <c r="B51" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -1710,22 +2616,28 @@
           <t>Bayern München</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n"/>
+      <c r="E51" s="2" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
       <c r="F51" s="6" t="n"/>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="21" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="15" t="n">
+      <c r="B52" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C52" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -1733,22 +2645,28 @@
           <t>Inter Milan</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n"/>
+      <c r="E52" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
       <c r="F52" s="6" t="n"/>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="2" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="21" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="15" t="n">
+      <c r="B53" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -1756,22 +2674,28 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n"/>
+      <c r="E53" s="2" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
       <c r="F53" s="6" t="n"/>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="2" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="21" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="15" t="n">
+      <c r="B54" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -1779,22 +2703,28 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n"/>
+      <c r="E54" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
       <c r="F54" s="6" t="n"/>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="2" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="21" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="15" t="n">
+      <c r="B55" s="3" t="n">
         <v>46316.875</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="4" t="n">
         <v>46316.875</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -1802,22 +2732,28 @@
           <t>Sporting Portugal</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n"/>
+      <c r="E55" s="2" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
       <c r="F55" s="6" t="n"/>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="2" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>LASK</t>
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="21" customHeight="1">
       <c r="A56" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="17" t="n">
+      <c r="B56" s="9" t="n">
         <v>46329.78125</v>
       </c>
-      <c r="C56" s="18" t="n">
+      <c r="C56" s="10" t="n">
         <v>46329.78125</v>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -1825,22 +2761,28 @@
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n"/>
+      <c r="E56" s="8" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
       <c r="F56" s="6" t="n"/>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="8" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>Sporting Portugal</t>
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="21" customHeight="1">
       <c r="A57" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B57" s="17" t="n">
+      <c r="B57" s="9" t="n">
         <v>46329.78125</v>
       </c>
-      <c r="C57" s="18" t="n">
+      <c r="C57" s="10" t="n">
         <v>46329.78125</v>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -1848,22 +2790,28 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n"/>
+      <c r="E57" s="8" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
       <c r="F57" s="6" t="n"/>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="8" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="21" customHeight="1">
       <c r="A58" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B58" s="17" t="n">
+      <c r="B58" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C58" s="18" t="n">
+      <c r="C58" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -1871,22 +2819,28 @@
           <t>Atlético Madrid</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n"/>
+      <c r="E58" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
       <c r="F58" s="6" t="n"/>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="8" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>Bayern München</t>
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="21" customHeight="1">
       <c r="A59" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B59" s="17" t="n">
+      <c r="B59" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C59" s="18" t="n">
+      <c r="C59" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -1894,22 +2848,28 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n"/>
+      <c r="E59" s="8" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
       <c r="F59" s="6" t="n"/>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="8" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="21" customHeight="1">
       <c r="A60" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B60" s="17" t="n">
+      <c r="B60" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C60" s="18" t="n">
+      <c r="C60" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -1917,22 +2877,28 @@
           <t>Feyenoord</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n"/>
+      <c r="E60" s="8" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
       <c r="F60" s="6" t="n"/>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="8" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
         <is>
           <t>Inter Milan</t>
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="21" customHeight="1">
       <c r="A61" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B61" s="17" t="n">
+      <c r="B61" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C61" s="18" t="n">
+      <c r="C61" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -1940,22 +2906,28 @@
           <t>Bodø/Glimt</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n"/>
+      <c r="E61" s="8" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
       <c r="F61" s="6" t="n"/>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="8" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="21" customHeight="1">
       <c r="A62" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B62" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C62" s="18" t="n">
+      <c r="C62" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -1963,22 +2935,28 @@
           <t>LASK</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n"/>
+      <c r="E62" s="8" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="F62" s="6" t="n"/>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="8" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
         <is>
           <t>Slovan Bratislava</t>
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="21" customHeight="1">
       <c r="A63" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B63" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C63" s="18" t="n">
+      <c r="C63" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -1986,22 +2964,28 @@
           <t>Manchester United</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n"/>
+      <c r="E63" s="8" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
       <c r="F63" s="6" t="n"/>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="8" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="21" customHeight="1">
       <c r="A64" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B64" s="17" t="n">
+      <c r="B64" s="9" t="n">
         <v>46329.875</v>
       </c>
-      <c r="C64" s="18" t="n">
+      <c r="C64" s="10" t="n">
         <v>46329.875</v>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -2009,22 +2993,28 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n"/>
+      <c r="E64" s="8" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
       <c r="F64" s="6" t="n"/>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="8" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="21" customHeight="1">
       <c r="A65" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B65" s="17" t="n">
+      <c r="B65" s="9" t="n">
         <v>46330.78125</v>
       </c>
-      <c r="C65" s="18" t="n">
+      <c r="C65" s="10" t="n">
         <v>46330.78125</v>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -2032,22 +3022,28 @@
           <t>AEK</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n"/>
+      <c r="E65" s="8" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F65" s="6" t="n"/>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="8" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="21" customHeight="1">
       <c r="A66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B66" s="17" t="n">
+      <c r="B66" s="9" t="n">
         <v>46330.78125</v>
       </c>
-      <c r="C66" s="18" t="n">
+      <c r="C66" s="10" t="n">
         <v>46330.78125</v>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -2055,22 +3051,28 @@
           <t>Fenerbahçe</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n"/>
+      <c r="E66" s="8" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
       <c r="F66" s="6" t="n"/>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="8" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="21" customHeight="1">
       <c r="A67" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B67" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C67" s="18" t="n">
+      <c r="C67" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -2078,22 +3080,28 @@
           <t>Borussia Dortmund</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n"/>
+      <c r="E67" s="8" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
       <c r="F67" s="6" t="n"/>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="8" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
         <is>
           <t>Betis</t>
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="21" customHeight="1">
       <c r="A68" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B68" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C68" s="18" t="n">
+      <c r="C68" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -2101,22 +3109,28 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n"/>
+      <c r="E68" s="8" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
       <c r="F68" s="6" t="n"/>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="8" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="21" customHeight="1">
       <c r="A69" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B69" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C69" s="18" t="n">
+      <c r="C69" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -2124,22 +3138,28 @@
           <t>PSV Eindhoven</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n"/>
+      <c r="E69" s="8" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
       <c r="F69" s="6" t="n"/>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="8" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
         <is>
           <t>Brugge</t>
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="21" customHeight="1">
       <c r="A70" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B70" s="17" t="n">
+      <c r="B70" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C70" s="18" t="n">
+      <c r="C70" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -2147,22 +3167,28 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n"/>
+      <c r="E70" s="8" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
       <c r="F70" s="6" t="n"/>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="8" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="21" customHeight="1">
       <c r="A71" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B71" s="17" t="n">
+      <c r="B71" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C71" s="18" t="n">
+      <c r="C71" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -2170,22 +3196,28 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n"/>
+      <c r="E71" s="8" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
       <c r="F71" s="6" t="n"/>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="8" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="21" customHeight="1">
       <c r="A72" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="17" t="n">
+      <c r="B72" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C72" s="18" t="n">
+      <c r="C72" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -2193,22 +3225,28 @@
           <t>Slavia Praha</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n"/>
+      <c r="E72" s="8" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
       <c r="F72" s="6" t="n"/>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="8" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="21" customHeight="1">
       <c r="A73" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B73" s="17" t="n">
+      <c r="B73" s="9" t="n">
         <v>46330.875</v>
       </c>
-      <c r="C73" s="18" t="n">
+      <c r="C73" s="10" t="n">
         <v>46330.875</v>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -2216,22 +3254,28 @@
           <t>Viking</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n"/>
+      <c r="E73" s="8" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
       <c r="F73" s="6" t="n"/>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="8" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
         <is>
           <t>Sabah</t>
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="21" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B74" s="15" t="n">
+      <c r="B74" s="3" t="n">
         <v>46350.78125</v>
       </c>
-      <c r="C74" s="16" t="n">
+      <c r="C74" s="4" t="n">
         <v>46350.78125</v>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2239,22 +3283,28 @@
           <t>Bodø/Glimt</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n"/>
+      <c r="E74" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
       <c r="F74" s="6" t="n"/>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="2" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>LASK</t>
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="21" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="15" t="n">
+      <c r="B75" s="3" t="n">
         <v>46350.78125</v>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="4" t="n">
         <v>46350.78125</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -2262,22 +3312,28 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n"/>
+      <c r="E75" s="2" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
       <c r="F75" s="6" t="n"/>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="21" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B76" s="15" t="n">
+      <c r="B76" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C76" s="16" t="n">
+      <c r="C76" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -2285,22 +3341,28 @@
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n"/>
+      <c r="E76" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
       <c r="F76" s="6" t="n"/>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="2" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="21" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B77" s="15" t="n">
+      <c r="B77" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C77" s="16" t="n">
+      <c r="C77" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -2308,22 +3370,28 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n"/>
+      <c r="E77" s="2" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
       <c r="F77" s="6" t="n"/>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>AEK</t>
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="21" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B78" s="15" t="n">
+      <c r="B78" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C78" s="16" t="n">
+      <c r="C78" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -2331,22 +3399,28 @@
           <t>Feyenoord</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n"/>
+      <c r="E78" s="2" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
       <c r="F78" s="6" t="n"/>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="2" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="21" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B79" s="15" t="n">
+      <c r="B79" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C79" s="16" t="n">
+      <c r="C79" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -2354,22 +3428,28 @@
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n"/>
+      <c r="E79" s="2" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
       <c r="F79" s="6" t="n"/>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G79" s="6" t="n"/>
+      <c r="H79" s="2" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="21" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B80" s="15" t="n">
+      <c r="B80" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C80" s="16" t="n">
+      <c r="C80" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -2377,22 +3457,28 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n"/>
+      <c r="E80" s="2" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
       <c r="F80" s="6" t="n"/>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="2" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="21" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="15" t="n">
+      <c r="B81" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C81" s="16" t="n">
+      <c r="C81" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -2400,22 +3486,28 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n"/>
+      <c r="E81" s="2" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
       <c r="F81" s="6" t="n"/>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="2" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="21" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B82" s="15" t="n">
+      <c r="B82" s="3" t="n">
         <v>46350.875</v>
       </c>
-      <c r="C82" s="16" t="n">
+      <c r="C82" s="4" t="n">
         <v>46350.875</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -2423,22 +3515,28 @@
           <t>Slovan Bratislava</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n"/>
+      <c r="E82" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
       <c r="F82" s="6" t="n"/>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Betis</t>
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="21" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="15" t="n">
+      <c r="B83" s="3" t="n">
         <v>46351.78125</v>
       </c>
-      <c r="C83" s="16" t="n">
+      <c r="C83" s="4" t="n">
         <v>46351.78125</v>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -2446,22 +3544,28 @@
           <t>Sabah</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n"/>
+      <c r="E83" s="2" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
       <c r="F83" s="6" t="n"/>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G83" s="6" t="n"/>
+      <c r="H83" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="21" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B84" s="15" t="n">
+      <c r="B84" s="3" t="n">
         <v>46351.78125</v>
       </c>
-      <c r="C84" s="16" t="n">
+      <c r="C84" s="4" t="n">
         <v>46351.78125</v>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -2469,22 +3573,28 @@
           <t>Slavia Praha</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n"/>
+      <c r="E84" s="2" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
       <c r="F84" s="6" t="n"/>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Villarreal</t>
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="21" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B85" s="15" t="n">
+      <c r="B85" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C85" s="16" t="n">
+      <c r="C85" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -2492,22 +3602,28 @@
           <t>Atlético Madrid</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n"/>
+      <c r="E85" s="2" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
       <c r="F85" s="6" t="n"/>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G85" s="6" t="n"/>
+      <c r="H85" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Viking</t>
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="21" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B86" s="15" t="n">
+      <c r="B86" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C86" s="16" t="n">
+      <c r="C86" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2515,22 +3631,28 @@
           <t>Brugge</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n"/>
+      <c r="E86" s="2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="F86" s="6" t="n"/>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="21" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="15" t="n">
+      <c r="B87" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C87" s="16" t="n">
+      <c r="C87" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -2538,22 +3660,28 @@
           <t>Inter Milan</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n"/>
+      <c r="E87" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
       <c r="F87" s="6" t="n"/>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="21" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B88" s="15" t="n">
+      <c r="B88" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C88" s="16" t="n">
+      <c r="C88" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2561,22 +3689,28 @@
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n"/>
+      <c r="E88" s="2" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
       <c r="F88" s="6" t="n"/>
-      <c r="G88" s="7" t="inlineStr">
+      <c r="G88" s="6" t="n"/>
+      <c r="H88" s="2" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="21" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B89" s="15" t="n">
+      <c r="B89" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C89" s="16" t="n">
+      <c r="C89" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -2584,22 +3718,28 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n"/>
+      <c r="E89" s="2" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
       <c r="F89" s="6" t="n"/>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="2" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>Bayern München</t>
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="21" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B90" s="15" t="n">
+      <c r="B90" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C90" s="16" t="n">
+      <c r="C90" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -2607,22 +3747,28 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n"/>
+      <c r="E90" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
       <c r="F90" s="6" t="n"/>
-      <c r="G90" s="7" t="inlineStr">
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="2" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="21" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B91" s="15" t="n">
+      <c r="B91" s="3" t="n">
         <v>46351.875</v>
       </c>
-      <c r="C91" s="16" t="n">
+      <c r="C91" s="4" t="n">
         <v>46351.875</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -2630,22 +3776,28 @@
           <t>Sporting Portugal</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n"/>
+      <c r="E91" s="2" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
       <c r="F91" s="6" t="n"/>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="2" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Manchester United</t>
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="21" customHeight="1">
       <c r="A92" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B92" s="17" t="n">
+      <c r="B92" s="9" t="n">
         <v>46364.78125</v>
       </c>
-      <c r="C92" s="18" t="n">
+      <c r="C92" s="10" t="n">
         <v>46364.78125</v>
       </c>
       <c r="D92" s="11" t="inlineStr">
@@ -2653,22 +3805,28 @@
           <t>Viking</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n"/>
+      <c r="E92" s="8" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
       <c r="F92" s="6" t="n"/>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="8" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="21" customHeight="1">
       <c r="A93" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B93" s="17" t="n">
+      <c r="B93" s="9" t="n">
         <v>46364.78125</v>
       </c>
-      <c r="C93" s="18" t="n">
+      <c r="C93" s="10" t="n">
         <v>46364.78125</v>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -2676,22 +3834,28 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n"/>
+      <c r="E93" s="8" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
       <c r="F93" s="6" t="n"/>
-      <c r="G93" s="12" t="inlineStr">
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="8" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
         <is>
           <t>Sabah</t>
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="21" customHeight="1">
       <c r="A94" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B94" s="17" t="n">
+      <c r="B94" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C94" s="18" t="n">
+      <c r="C94" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D94" s="11" t="inlineStr">
@@ -2699,22 +3863,28 @@
           <t>AEK</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n"/>
+      <c r="E94" s="8" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F94" s="6" t="n"/>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G94" s="6" t="n"/>
+      <c r="H94" s="8" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
         <is>
           <t>Galatasaray</t>
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="21" customHeight="1">
       <c r="A95" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B95" s="17" t="n">
+      <c r="B95" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C95" s="18" t="n">
+      <c r="C95" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -2722,22 +3892,28 @@
           <t>Roma</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n"/>
+      <c r="E95" s="8" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
       <c r="F95" s="6" t="n"/>
-      <c r="G95" s="12" t="inlineStr">
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="8" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
         <is>
           <t>Sporting Portugal</t>
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="21" customHeight="1">
       <c r="A96" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B96" s="17" t="n">
+      <c r="B96" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C96" s="18" t="n">
+      <c r="C96" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -2745,22 +3921,28 @@
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n"/>
+      <c r="E96" s="8" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
       <c r="F96" s="6" t="n"/>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G96" s="6" t="n"/>
+      <c r="H96" s="8" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="21" customHeight="1">
       <c r="A97" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B97" s="17" t="n">
+      <c r="B97" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C97" s="18" t="n">
+      <c r="C97" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -2768,22 +3950,28 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n"/>
+      <c r="E97" s="8" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
       <c r="F97" s="6" t="n"/>
-      <c r="G97" s="12" t="inlineStr">
+      <c r="G97" s="6" t="n"/>
+      <c r="H97" s="8" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="21" customHeight="1">
       <c r="A98" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B98" s="17" t="n">
+      <c r="B98" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C98" s="18" t="n">
+      <c r="C98" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -2791,22 +3979,28 @@
           <t>Bayern München</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n"/>
+      <c r="E98" s="8" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
       <c r="F98" s="6" t="n"/>
-      <c r="G98" s="12" t="inlineStr">
+      <c r="G98" s="6" t="n"/>
+      <c r="H98" s="8" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
         <is>
           <t>Slavia Praha</t>
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="21" customHeight="1">
       <c r="A99" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B99" s="17" t="n">
+      <c r="B99" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C99" s="18" t="n">
+      <c r="C99" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -2814,22 +4008,28 @@
           <t>Manchester United</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n"/>
+      <c r="E99" s="8" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
       <c r="F99" s="6" t="n"/>
-      <c r="G99" s="12" t="inlineStr">
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="8" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="21" customHeight="1">
       <c r="A100" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B100" s="17" t="n">
+      <c r="B100" s="9" t="n">
         <v>46364.875</v>
       </c>
-      <c r="C100" s="18" t="n">
+      <c r="C100" s="10" t="n">
         <v>46364.875</v>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -2837,22 +4037,28 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n"/>
+      <c r="E100" s="8" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
       <c r="F100" s="6" t="n"/>
-      <c r="G100" s="12" t="inlineStr">
+      <c r="G100" s="6" t="n"/>
+      <c r="H100" s="8" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
         <is>
           <t>Brugge</t>
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="21" customHeight="1">
       <c r="A101" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B101" s="17" t="n">
+      <c r="B101" s="9" t="n">
         <v>46365.78125</v>
       </c>
-      <c r="C101" s="18" t="n">
+      <c r="C101" s="10" t="n">
         <v>46365.78125</v>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -2860,22 +4066,28 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="E101" s="6" t="n"/>
+      <c r="E101" s="8" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
       <c r="F101" s="6" t="n"/>
-      <c r="G101" s="12" t="inlineStr">
+      <c r="G101" s="6" t="n"/>
+      <c r="H101" s="8" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="21" customHeight="1">
       <c r="A102" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B102" s="17" t="n">
+      <c r="B102" s="9" t="n">
         <v>46365.78125</v>
       </c>
-      <c r="C102" s="18" t="n">
+      <c r="C102" s="10" t="n">
         <v>46365.78125</v>
       </c>
       <c r="D102" s="11" t="inlineStr">
@@ -2883,22 +4095,28 @@
           <t>Slovan Bratislava</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n"/>
+      <c r="E102" s="8" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
       <c r="F102" s="6" t="n"/>
-      <c r="G102" s="12" t="inlineStr">
+      <c r="G102" s="6" t="n"/>
+      <c r="H102" s="8" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="21" customHeight="1">
       <c r="A103" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B103" s="17" t="n">
+      <c r="B103" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C103" s="18" t="n">
+      <c r="C103" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D103" s="11" t="inlineStr">
@@ -2906,22 +4124,28 @@
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="E103" s="6" t="n"/>
+      <c r="E103" s="8" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
       <c r="F103" s="6" t="n"/>
-      <c r="G103" s="12" t="inlineStr">
+      <c r="G103" s="6" t="n"/>
+      <c r="H103" s="8" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="21" customHeight="1">
       <c r="A104" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B104" s="17" t="n">
+      <c r="B104" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C104" s="18" t="n">
+      <c r="C104" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D104" s="11" t="inlineStr">
@@ -2929,22 +4153,28 @@
           <t>Borussia Dortmund</t>
         </is>
       </c>
-      <c r="E104" s="6" t="n"/>
+      <c r="E104" s="8" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
       <c r="F104" s="6" t="n"/>
-      <c r="G104" s="12" t="inlineStr">
+      <c r="G104" s="6" t="n"/>
+      <c r="H104" s="8" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
         <is>
           <t>Inter Milan</t>
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="21" customHeight="1">
       <c r="A105" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B105" s="17" t="n">
+      <c r="B105" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C105" s="18" t="n">
+      <c r="C105" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D105" s="11" t="inlineStr">
@@ -2952,22 +4182,28 @@
           <t>LASK</t>
         </is>
       </c>
-      <c r="E105" s="6" t="n"/>
+      <c r="E105" s="8" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="F105" s="6" t="n"/>
-      <c r="G105" s="12" t="inlineStr">
+      <c r="G105" s="6" t="n"/>
+      <c r="H105" s="8" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="21" customHeight="1">
       <c r="A106" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B106" s="17" t="n">
+      <c r="B106" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C106" s="18" t="n">
+      <c r="C106" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D106" s="11" t="inlineStr">
@@ -2975,22 +4211,28 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="E106" s="6" t="n"/>
+      <c r="E106" s="8" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
       <c r="F106" s="6" t="n"/>
-      <c r="G106" s="12" t="inlineStr">
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="8" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="21" customHeight="1">
       <c r="A107" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B107" s="17" t="n">
+      <c r="B107" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C107" s="18" t="n">
+      <c r="C107" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D107" s="11" t="inlineStr">
@@ -2998,22 +4240,28 @@
           <t>PSV Eindhoven</t>
         </is>
       </c>
-      <c r="E107" s="6" t="n"/>
+      <c r="E107" s="8" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
       <c r="F107" s="6" t="n"/>
-      <c r="G107" s="12" t="inlineStr">
+      <c r="G107" s="6" t="n"/>
+      <c r="H107" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="21" customHeight="1">
       <c r="A108" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B108" s="17" t="n">
+      <c r="B108" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C108" s="18" t="n">
+      <c r="C108" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D108" s="11" t="inlineStr">
@@ -3021,22 +4269,28 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="E108" s="6" t="n"/>
+      <c r="E108" s="8" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
       <c r="F108" s="6" t="n"/>
-      <c r="G108" s="12" t="inlineStr">
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="8" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="21" customHeight="1">
       <c r="A109" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B109" s="17" t="n">
+      <c r="B109" s="9" t="n">
         <v>46365.875</v>
       </c>
-      <c r="C109" s="18" t="n">
+      <c r="C109" s="10" t="n">
         <v>46365.875</v>
       </c>
       <c r="D109" s="11" t="inlineStr">
@@ -3044,22 +4298,28 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="E109" s="6" t="n"/>
+      <c r="E109" s="8" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
       <c r="F109" s="6" t="n"/>
-      <c r="G109" s="12" t="inlineStr">
+      <c r="G109" s="6" t="n"/>
+      <c r="H109" s="8" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="21" customHeight="1">
       <c r="A110" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B110" s="15" t="n">
+      <c r="B110" s="3" t="n">
         <v>46406.78125</v>
       </c>
-      <c r="C110" s="16" t="n">
+      <c r="C110" s="4" t="n">
         <v>46406.78125</v>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -3067,22 +4327,28 @@
           <t>Bodø/Glimt</t>
         </is>
       </c>
-      <c r="E110" s="6" t="n"/>
+      <c r="E110" s="2" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
       <c r="F110" s="6" t="n"/>
-      <c r="G110" s="7" t="inlineStr">
+      <c r="G110" s="6" t="n"/>
+      <c r="H110" s="2" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I110" s="7" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="21" customHeight="1">
       <c r="A111" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B111" s="15" t="n">
+      <c r="B111" s="3" t="n">
         <v>46406.78125</v>
       </c>
-      <c r="C111" s="16" t="n">
+      <c r="C111" s="4" t="n">
         <v>46406.78125</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -3090,22 +4356,28 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="E111" s="6" t="n"/>
+      <c r="E111" s="2" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
       <c r="F111" s="6" t="n"/>
-      <c r="G111" s="7" t="inlineStr">
+      <c r="G111" s="6" t="n"/>
+      <c r="H111" s="2" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="21" customHeight="1">
       <c r="A112" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B112" s="15" t="n">
+      <c r="B112" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C112" s="16" t="n">
+      <c r="C112" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -3113,22 +4385,28 @@
           <t>AEK</t>
         </is>
       </c>
-      <c r="E112" s="6" t="n"/>
+      <c r="E112" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F112" s="6" t="n"/>
-      <c r="G112" s="7" t="inlineStr">
+      <c r="G112" s="6" t="n"/>
+      <c r="H112" s="2" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I112" s="7" t="inlineStr">
         <is>
           <t>Roma</t>
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="21" customHeight="1">
       <c r="A113" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B113" s="15" t="n">
+      <c r="B113" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C113" s="16" t="n">
+      <c r="C113" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -3136,22 +4414,28 @@
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="E113" s="6" t="n"/>
+      <c r="E113" s="2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
       <c r="F113" s="6" t="n"/>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="G113" s="6" t="n"/>
+      <c r="H113" s="2" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I113" s="7" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="21" customHeight="1">
       <c r="A114" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B114" s="15" t="n">
+      <c r="B114" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C114" s="16" t="n">
+      <c r="C114" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -3159,22 +4443,28 @@
           <t>Inter Milan</t>
         </is>
       </c>
-      <c r="E114" s="6" t="n"/>
+      <c r="E114" s="2" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
       <c r="F114" s="6" t="n"/>
-      <c r="G114" s="7" t="inlineStr">
+      <c r="G114" s="6" t="n"/>
+      <c r="H114" s="2" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I114" s="7" t="inlineStr">
         <is>
           <t>Liverpool</t>
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="21" customHeight="1">
       <c r="A115" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B115" s="15" t="n">
+      <c r="B115" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C115" s="16" t="n">
+      <c r="C115" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -3182,22 +4472,28 @@
           <t>Porto</t>
         </is>
       </c>
-      <c r="E115" s="6" t="n"/>
+      <c r="E115" s="2" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
       <c r="F115" s="6" t="n"/>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G115" s="6" t="n"/>
+      <c r="H115" s="2" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I115" s="7" t="inlineStr">
         <is>
           <t>Slavia Praha</t>
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="21" customHeight="1">
       <c r="A116" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B116" s="15" t="n">
+      <c r="B116" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C116" s="16" t="n">
+      <c r="C116" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -3205,22 +4501,28 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="E116" s="6" t="n"/>
+      <c r="E116" s="2" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
       <c r="F116" s="6" t="n"/>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G116" s="6" t="n"/>
+      <c r="H116" s="2" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I116" s="7" t="inlineStr">
         <is>
           <t>Slovan Bratislava</t>
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="21" customHeight="1">
       <c r="A117" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B117" s="15" t="n">
+      <c r="B117" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C117" s="16" t="n">
+      <c r="C117" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -3228,22 +4530,28 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="E117" s="6" t="n"/>
+      <c r="E117" s="2" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
       <c r="F117" s="6" t="n"/>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G117" s="6" t="n"/>
+      <c r="H117" s="2" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I117" s="7" t="inlineStr">
         <is>
           <t>LASK</t>
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="21" customHeight="1">
       <c r="A118" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="15" t="n">
+      <c r="B118" s="3" t="n">
         <v>46406.875</v>
       </c>
-      <c r="C118" s="16" t="n">
+      <c r="C118" s="4" t="n">
         <v>46406.875</v>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -3251,22 +4559,28 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="E118" s="6" t="n"/>
+      <c r="E118" s="2" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
       <c r="F118" s="6" t="n"/>
-      <c r="G118" s="7" t="inlineStr">
+      <c r="G118" s="6" t="n"/>
+      <c r="H118" s="2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
         <is>
           <t>Brugge</t>
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="21" customHeight="1">
       <c r="A119" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B119" s="15" t="n">
+      <c r="B119" s="3" t="n">
         <v>46407.78125</v>
       </c>
-      <c r="C119" s="16" t="n">
+      <c r="C119" s="4" t="n">
         <v>46407.78125</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -3274,22 +4588,28 @@
           <t>Fenerbahçe</t>
         </is>
       </c>
-      <c r="E119" s="6" t="n"/>
+      <c r="E119" s="2" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
       <c r="F119" s="6" t="n"/>
-      <c r="G119" s="7" t="inlineStr">
+      <c r="G119" s="6" t="n"/>
+      <c r="H119" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I119" s="7" t="inlineStr">
         <is>
           <t>Villarreal</t>
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="21" customHeight="1">
       <c r="A120" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B120" s="15" t="n">
+      <c r="B120" s="3" t="n">
         <v>46407.78125</v>
       </c>
-      <c r="C120" s="16" t="n">
+      <c r="C120" s="4" t="n">
         <v>46407.78125</v>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -3297,22 +4617,28 @@
           <t>Sabah</t>
         </is>
       </c>
-      <c r="E120" s="6" t="n"/>
+      <c r="E120" s="2" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
       <c r="F120" s="6" t="n"/>
-      <c r="G120" s="7" t="inlineStr">
+      <c r="G120" s="6" t="n"/>
+      <c r="H120" s="2" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="21" customHeight="1">
       <c r="A121" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B121" s="15" t="n">
+      <c r="B121" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C121" s="16" t="n">
+      <c r="C121" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -3320,22 +4646,28 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="E121" s="6" t="n"/>
+      <c r="E121" s="2" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
       <c r="F121" s="6" t="n"/>
-      <c r="G121" s="7" t="inlineStr">
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="2" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I121" s="7" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="21" customHeight="1">
       <c r="A122" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B122" s="15" t="n">
+      <c r="B122" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C122" s="16" t="n">
+      <c r="C122" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -3343,22 +4675,28 @@
           <t>Manchester United</t>
         </is>
       </c>
-      <c r="E122" s="6" t="n"/>
+      <c r="E122" s="2" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
       <c r="F122" s="6" t="n"/>
-      <c r="G122" s="7" t="inlineStr">
+      <c r="G122" s="6" t="n"/>
+      <c r="H122" s="2" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I122" s="7" t="inlineStr">
         <is>
           <t>Bayern München</t>
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="21" customHeight="1">
       <c r="A123" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B123" s="15" t="n">
+      <c r="B123" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C123" s="16" t="n">
+      <c r="C123" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -3366,22 +4704,28 @@
           <t>Leipzig</t>
         </is>
       </c>
-      <c r="E123" s="6" t="n"/>
+      <c r="E123" s="2" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
       <c r="F123" s="6" t="n"/>
-      <c r="G123" s="7" t="inlineStr">
+      <c r="G123" s="6" t="n"/>
+      <c r="H123" s="2" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I123" s="7" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="21" customHeight="1">
       <c r="A124" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B124" s="15" t="n">
+      <c r="B124" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C124" s="16" t="n">
+      <c r="C124" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -3389,22 +4733,28 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="E124" s="6" t="n"/>
+      <c r="E124" s="2" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
       <c r="F124" s="6" t="n"/>
-      <c r="G124" s="7" t="inlineStr">
+      <c r="G124" s="6" t="n"/>
+      <c r="H124" s="2" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="21" customHeight="1">
       <c r="A125" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B125" s="15" t="n">
+      <c r="B125" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C125" s="16" t="n">
+      <c r="C125" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -3412,22 +4762,28 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="E125" s="6" t="n"/>
+      <c r="E125" s="2" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
       <c r="F125" s="6" t="n"/>
-      <c r="G125" s="7" t="inlineStr">
+      <c r="G125" s="6" t="n"/>
+      <c r="H125" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I125" s="7" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="21" customHeight="1">
       <c r="A126" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B126" s="15" t="n">
+      <c r="B126" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C126" s="16" t="n">
+      <c r="C126" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -3435,22 +4791,28 @@
           <t>Sporting Portugal</t>
         </is>
       </c>
-      <c r="E126" s="6" t="n"/>
+      <c r="E126" s="2" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
       <c r="F126" s="6" t="n"/>
-      <c r="G126" s="7" t="inlineStr">
+      <c r="G126" s="6" t="n"/>
+      <c r="H126" s="2" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="21" customHeight="1">
       <c r="A127" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B127" s="15" t="n">
+      <c r="B127" s="3" t="n">
         <v>46407.875</v>
       </c>
-      <c r="C127" s="16" t="n">
+      <c r="C127" s="4" t="n">
         <v>46407.875</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -3458,22 +4820,28 @@
           <t>Viking</t>
         </is>
       </c>
-      <c r="E127" s="6" t="n"/>
+      <c r="E127" s="2" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
       <c r="F127" s="6" t="n"/>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G127" s="6" t="n"/>
+      <c r="H127" s="2" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="21" customHeight="1">
       <c r="A128" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B128" s="17" t="n">
+      <c r="B128" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C128" s="18" t="n">
+      <c r="C128" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D128" s="11" t="inlineStr">
@@ -3481,22 +4849,28 @@
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="E128" s="6" t="n"/>
+      <c r="E128" s="8" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
       <c r="F128" s="6" t="n"/>
-      <c r="G128" s="12" t="inlineStr">
+      <c r="G128" s="6" t="n"/>
+      <c r="H128" s="8" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
         <is>
           <t>Sabah</t>
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="21" customHeight="1">
       <c r="A129" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B129" s="17" t="n">
+      <c r="B129" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C129" s="18" t="n">
+      <c r="C129" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D129" s="11" t="inlineStr">
@@ -3504,22 +4878,28 @@
           <t>Roma</t>
         </is>
       </c>
-      <c r="E129" s="6" t="n"/>
+      <c r="E129" s="8" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
       <c r="F129" s="6" t="n"/>
-      <c r="G129" s="12" t="inlineStr">
+      <c r="G129" s="6" t="n"/>
+      <c r="H129" s="8" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="21" customHeight="1">
       <c r="A130" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B130" s="17" t="n">
+      <c r="B130" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C130" s="18" t="n">
+      <c r="C130" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D130" s="11" t="inlineStr">
@@ -3527,22 +4907,28 @@
           <t>Atlético Madrid</t>
         </is>
       </c>
-      <c r="E130" s="6" t="n"/>
+      <c r="E130" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
       <c r="F130" s="6" t="n"/>
-      <c r="G130" s="12" t="inlineStr">
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="8" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="21" customHeight="1">
       <c r="A131" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B131" s="17" t="n">
+      <c r="B131" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C131" s="18" t="n">
+      <c r="C131" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D131" s="11" t="inlineStr">
@@ -3550,22 +4936,28 @@
           <t>Borussia Dortmund</t>
         </is>
       </c>
-      <c r="E131" s="6" t="n"/>
+      <c r="E131" s="8" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
       <c r="F131" s="6" t="n"/>
-      <c r="G131" s="12" t="inlineStr">
+      <c r="G131" s="6" t="n"/>
+      <c r="H131" s="8" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
         <is>
           <t>AEK</t>
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="21" customHeight="1">
       <c r="A132" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B132" s="17" t="n">
+      <c r="B132" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C132" s="18" t="n">
+      <c r="C132" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D132" s="11" t="inlineStr">
@@ -3573,22 +4965,28 @@
           <t>Brugge</t>
         </is>
       </c>
-      <c r="E132" s="6" t="n"/>
+      <c r="E132" s="8" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="F132" s="6" t="n"/>
-      <c r="G132" s="12" t="inlineStr">
+      <c r="G132" s="6" t="n"/>
+      <c r="H132" s="8" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I132" s="12" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="21" customHeight="1">
       <c r="A133" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B133" s="17" t="n">
+      <c r="B133" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C133" s="18" t="n">
+      <c r="C133" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -3596,22 +4994,28 @@
           <t>Bayern München</t>
         </is>
       </c>
-      <c r="E133" s="6" t="n"/>
+      <c r="E133" s="8" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
       <c r="F133" s="6" t="n"/>
-      <c r="G133" s="12" t="inlineStr">
+      <c r="G133" s="6" t="n"/>
+      <c r="H133" s="8" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I133" s="12" t="inlineStr">
         <is>
           <t>Betis</t>
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="21" customHeight="1">
       <c r="A134" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B134" s="17" t="n">
+      <c r="B134" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C134" s="18" t="n">
+      <c r="C134" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D134" s="11" t="inlineStr">
@@ -3619,22 +5023,28 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E134" s="6" t="n"/>
+      <c r="E134" s="8" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
       <c r="F134" s="6" t="n"/>
-      <c r="G134" s="12" t="inlineStr">
+      <c r="G134" s="6" t="n"/>
+      <c r="H134" s="8" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="21" customHeight="1">
       <c r="A135" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B135" s="17" t="n">
+      <c r="B135" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C135" s="18" t="n">
+      <c r="C135" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D135" s="11" t="inlineStr">
@@ -3642,22 +5052,28 @@
           <t>Shakhtar Donetsk</t>
         </is>
       </c>
-      <c r="E135" s="6" t="n"/>
+      <c r="E135" s="8" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
       <c r="F135" s="6" t="n"/>
-      <c r="G135" s="12" t="inlineStr">
+      <c r="G135" s="6" t="n"/>
+      <c r="H135" s="8" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I135" s="12" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="21" customHeight="1">
       <c r="A136" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B136" s="17" t="n">
+      <c r="B136" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C136" s="18" t="n">
+      <c r="C136" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D136" s="11" t="inlineStr">
@@ -3665,22 +5081,28 @@
           <t>Feyenoord</t>
         </is>
       </c>
-      <c r="E136" s="6" t="n"/>
+      <c r="E136" s="8" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
       <c r="F136" s="6" t="n"/>
-      <c r="G136" s="12" t="inlineStr">
+      <c r="G136" s="6" t="n"/>
+      <c r="H136" s="8" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I136" s="12" t="inlineStr">
         <is>
           <t>Leipzig</t>
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="21" customHeight="1">
       <c r="A137" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B137" s="17" t="n">
+      <c r="B137" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C137" s="18" t="n">
+      <c r="C137" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -3688,22 +5110,28 @@
           <t>LASK</t>
         </is>
       </c>
-      <c r="E137" s="6" t="n"/>
+      <c r="E137" s="8" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="F137" s="6" t="n"/>
-      <c r="G137" s="12" t="inlineStr">
+      <c r="G137" s="6" t="n"/>
+      <c r="H137" s="8" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="21" customHeight="1">
       <c r="A138" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B138" s="17" t="n">
+      <c r="B138" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C138" s="18" t="n">
+      <c r="C138" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D138" s="11" t="inlineStr">
@@ -3711,22 +5139,28 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="E138" s="6" t="n"/>
+      <c r="E138" s="8" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
       <c r="F138" s="6" t="n"/>
-      <c r="G138" s="12" t="inlineStr">
+      <c r="G138" s="6" t="n"/>
+      <c r="H138" s="8" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="21" customHeight="1">
       <c r="A139" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B139" s="17" t="n">
+      <c r="B139" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C139" s="18" t="n">
+      <c r="C139" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D139" s="11" t="inlineStr">
@@ -3734,22 +5168,28 @@
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="E139" s="6" t="n"/>
+      <c r="E139" s="8" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
       <c r="F139" s="6" t="n"/>
-      <c r="G139" s="12" t="inlineStr">
+      <c r="G139" s="6" t="n"/>
+      <c r="H139" s="8" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
         <is>
           <t>Sporting Portugal</t>
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="21" customHeight="1">
       <c r="A140" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B140" s="17" t="n">
+      <c r="B140" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C140" s="18" t="n">
+      <c r="C140" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D140" s="11" t="inlineStr">
@@ -3757,22 +5197,28 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="E140" s="6" t="n"/>
+      <c r="E140" s="8" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
       <c r="F140" s="6" t="n"/>
-      <c r="G140" s="12" t="inlineStr">
+      <c r="G140" s="6" t="n"/>
+      <c r="H140" s="8" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I140" s="12" t="inlineStr">
         <is>
           <t>Galatasaray</t>
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="21" customHeight="1">
       <c r="A141" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B141" s="17" t="n">
+      <c r="B141" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C141" s="18" t="n">
+      <c r="C141" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D141" s="11" t="inlineStr">
@@ -3780,22 +5226,28 @@
           <t>PSV Eindhoven</t>
         </is>
       </c>
-      <c r="E141" s="6" t="n"/>
+      <c r="E141" s="8" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
       <c r="F141" s="6" t="n"/>
-      <c r="G141" s="12" t="inlineStr">
+      <c r="G141" s="6" t="n"/>
+      <c r="H141" s="8" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="21" customHeight="1">
       <c r="A142" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B142" s="17" t="n">
+      <c r="B142" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C142" s="18" t="n">
+      <c r="C142" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D142" s="11" t="inlineStr">
@@ -3803,22 +5255,28 @@
           <t>Slavia Praha</t>
         </is>
       </c>
-      <c r="E142" s="6" t="n"/>
+      <c r="E142" s="8" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
       <c r="F142" s="6" t="n"/>
-      <c r="G142" s="12" t="inlineStr">
+      <c r="G142" s="6" t="n"/>
+      <c r="H142" s="8" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I142" s="12" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="21" customHeight="1">
       <c r="A143" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B143" s="17" t="n">
+      <c r="B143" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C143" s="18" t="n">
+      <c r="C143" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D143" s="11" t="inlineStr">
@@ -3826,22 +5284,28 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="E143" s="6" t="n"/>
+      <c r="E143" s="8" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
       <c r="F143" s="6" t="n"/>
-      <c r="G143" s="12" t="inlineStr">
+      <c r="G143" s="6" t="n"/>
+      <c r="H143" s="8" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I143" s="12" t="inlineStr">
         <is>
           <t>Viking</t>
         </is>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="21" customHeight="1">
       <c r="A144" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B144" s="17" t="n">
+      <c r="B144" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C144" s="18" t="n">
+      <c r="C144" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D144" s="11" t="inlineStr">
@@ -3849,22 +5313,28 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="E144" s="6" t="n"/>
+      <c r="E144" s="8" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
       <c r="F144" s="6" t="n"/>
-      <c r="G144" s="12" t="inlineStr">
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="8" t="e" vm="33">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
         <is>
           <t>Manchester United</t>
         </is>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="21" customHeight="1">
       <c r="A145" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B145" s="17" t="n">
+      <c r="B145" s="9" t="n">
         <v>46414.875</v>
       </c>
-      <c r="C145" s="18" t="n">
+      <c r="C145" s="10" t="n">
         <v>46414.875</v>
       </c>
       <c r="D145" s="11" t="inlineStr">
@@ -3872,9 +5342,15 @@
           <t>Slovan Bratislava</t>
         </is>
       </c>
-      <c r="E145" s="6" t="n"/>
+      <c r="E145" s="8" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
       <c r="F145" s="6" t="n"/>
-      <c r="G145" s="12" t="inlineStr">
+      <c r="G145" s="6" t="n"/>
+      <c r="H145" s="8" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
         <is>
           <t>Inter Milan</t>
         </is>
@@ -3897,21 +5373,21 @@
     <row r="149">
       <c r="A149" s="14" t="inlineStr">
         <is>
-          <t>Las columnas "Gol" (celdas amarillas) están vacías en el origen: son las casillas donde se introducen los resultados.</t>
+          <t>Los escudos son los mismos del archivo original: imágenes dentro de la celda, por lo que acompañan a la fila al ordenar o filtrar.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>Fecha y hora se muestran tal y como estaban calculadas en el archivo original (horario CET, el que traía el fichero).</t>
+          <t>Las columnas "Gol" (celdas amarillas) están vacías en el origen: son las casillas donde se introducen los resultados.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="inlineStr">
         <is>
-          <t>Se han omitido las columnas de escudos (Badge) y los indicadores "P" del original, porque dependen de imágenes y fórmulas internas del libro de origen.</t>
+          <t>Fecha y hora se muestran tal y como estaban calculadas en el archivo original (horario CET, el que traía el fichero).</t>
         </is>
       </c>
     </row>
@@ -3923,7 +5399,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G145"/>
+  <autoFilter ref="A1:I145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>